--- a/backtest_runs/20260410_193731/by_symbol/UBDL/UBDL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/UBDL/UBDL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-1630.590000000004</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>104230.72</v>
@@ -679,7 +679,7 @@
         <v>-4407</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>99823.72</v>
@@ -771,7 +771,7 @@
         <v>-3481.529999999996</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>104671.42</v>
@@ -863,7 +863,7 @@
         <v>-4935.840000000005</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>105552.82</v>
@@ -955,7 +955,7 @@
         <v>-2688.269999999998</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>102864.55</v>
@@ -1093,7 +1093,7 @@
         <v>-5464.680000000008</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>97399.87</v>
@@ -1185,7 +1185,7 @@
         <v>-2247.570000000007</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>102027.22</v>
@@ -1277,7 +1277,7 @@
         <v>-3790.019999999998</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>102600.13</v>
@@ -1415,7 +1415,7 @@
         <v>-3834.089999999989</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>101674.66</v>
@@ -1507,7 +1507,7 @@
         <v>-1895.009999999999</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>106654.57</v>
@@ -1553,7 +1553,7 @@
         <v>-7183.409999999995</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>99471.16000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-2644.200000000006</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>103790.02</v>
